--- a/Mantenimiento/excels/JUNIN-HUANCAYO-CHILCA.xlsx
+++ b/Mantenimiento/excels/JUNIN-HUANCAYO-CHILCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1107,11 +1047,6 @@
       </c>
       <c r="K13" t="n">
         <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/JUNIN-HUANCAYO-CHILCA.xlsx
+++ b/Mantenimiento/excels/JUNIN-HUANCAYO-CHILCA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>30012 VICTOR ALBERTO GIL MALLMA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.07839</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-75.19661000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>969</v>
-      </c>
-      <c r="J2" t="n">
-        <v>54</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.07839</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-75.19661</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>30153 MARIA N. SALAZAR AGUILAR</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.088048</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-75.19954300000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>852</v>
-      </c>
-      <c r="J3" t="n">
-        <v>48</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.088048</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-75.199543</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>30154 INMACULADO CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.08095</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-75.20560999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>569</v>
-      </c>
-      <c r="J4" t="n">
-        <v>31</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.08095</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-75.20561</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>30155 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.08608</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-75.21057999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>676</v>
-      </c>
-      <c r="J5" t="n">
-        <v>33</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.08608</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-75.21058</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>31543 TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.0962548958917</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-75.1913272190753</v>
-      </c>
-      <c r="I6" t="n">
-        <v>885</v>
-      </c>
-      <c r="J6" t="n">
-        <v>39</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.0962548958917</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-75.1913272190753</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>BERNARD BLENKIR</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.09042</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-75.20526</v>
-      </c>
-      <c r="I7" t="n">
-        <v>534</v>
-      </c>
-      <c r="J7" t="n">
-        <v>13</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.09042</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-75.20526</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>WINNER</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.08627</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-75.20153999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>155</v>
-      </c>
-      <c r="J8" t="n">
-        <v>17</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.08627</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-75.20154</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>ANGELITOS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.08368</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-75.20295</v>
-      </c>
-      <c r="I9" t="n">
-        <v>15</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.08368</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-75.20295</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>MOODY</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.081641</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-75.199522</v>
-      </c>
-      <c r="I10" t="n">
-        <v>550</v>
-      </c>
-      <c r="J10" t="n">
-        <v>29</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.081641</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-75.199522</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>ORION INTERNACIONAL</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.082508</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-75.20286299999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>392</v>
-      </c>
-      <c r="J11" t="n">
-        <v>31</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.082508</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-75.202863</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>UNION INTERNACIONAL</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.07737</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-75.197005</v>
-      </c>
-      <c r="I12" t="n">
-        <v>353</v>
-      </c>
-      <c r="J12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.07737</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-75.197005</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>BLENKIR AUQUIMARCA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.084903</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-75.21595499999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>187</v>
-      </c>
-      <c r="J13" t="n">
-        <v>11</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.084903</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-75.215955</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
